--- a/questionnaire/sources.xlsx
+++ b/questionnaire/sources.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="735" windowWidth="12960" windowHeight="5865" tabRatio="831" firstSheet="2" activeTab="14"/>
+    <workbookView minimized="1" xWindow="0" yWindow="735" windowWidth="12960" windowHeight="5865" tabRatio="831" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Figures" sheetId="1" r:id="rId1"/>
@@ -54,6 +54,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source : https://www.eea.europa.eu/data-and-maps/data/external/degree-of-urbanisation-degurba</t>
@@ -67,6 +68,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source(year 2025) : INSEE
@@ -81,6 +83,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source(year 2025) : INSEE
@@ -97,6 +100,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source(year 2025) : INSEE
@@ -113,6 +117,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Year 2025
@@ -127,6 +132,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -141,6 +147,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">2015 data - best available
@@ -156,6 +163,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Ile de France
@@ -172,6 +180,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">North and East
@@ -187,6 +196,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>South West
@@ -201,6 +211,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>South-East
@@ -215,6 +226,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Other regions
@@ -229,6 +241,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -244,6 +257,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -259,6 +273,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">2023
@@ -274,6 +289,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -299,6 +315,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -313,6 +330,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
@@ -327,6 +345,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -341,6 +360,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -355,6 +375,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -369,6 +390,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">% Inscrits
@@ -383,6 +405,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">same definition as 2020
@@ -397,6 +420,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2023) : Destatis Statistisches Bundesamt
@@ -411,6 +435,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source : (Year 2023)
@@ -425,6 +450,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -439,6 +465,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -453,6 +480,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -467,6 +495,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -481,6 +510,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -495,6 +525,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -509,6 +540,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en</t>
@@ -522,6 +554,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
@@ -539,6 +572,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Southern
@@ -554,6 +588,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">3 -Others [Northern, Western, Central]
@@ -569,6 +604,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://data-explorer.oecd.org/vis?tm=inactivity&amp;pg=0&amp;snb=17&amp;vw=tb&amp;df[ds]=dsDisseminateFinalDMZ&amp;df[id]=DSD_EAG_LSO_EA%40DF_LSO_NEAC_INAC&amp;df[ag]=OECD.EDU.IMEP&amp;df[vs]=1.0&amp;dq=FRA%2BDEU%2BITA%2BJPN%2BLVA%2BMEX%2BPOL%2BESP%2BCHE%2BGBR%2BUSA%2BOECD%2BIND%2BROU%2BZAF._T.Y25T64._T..........OBS...A&amp;lom=LASTNOBSERVATIONS&amp;lo=1&amp;pd=2020%2C2023&amp;to[TIME_PERIOD]=true</t>
@@ -582,6 +618,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -596,6 +633,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Bundestagswahl 2025 : 
@@ -627,6 +665,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Bundestagswahl 2025 : </t>
@@ -640,6 +679,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Bundestagswahl 2025 : </t>
@@ -653,6 +693,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Bundestagswahl 2025 : 
@@ -684,6 +725,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Center-right or right
@@ -712,6 +754,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Far right
@@ -728,6 +771,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Abstention = Persons entitled to vote
@@ -744,6 +788,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -758,6 +803,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  Istituto Nazionale di Statistica
@@ -778,6 +824,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -797,6 +844,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -811,6 +859,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -825,6 +874,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -839,6 +889,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -853,6 +904,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -867,6 +919,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -881,6 +934,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en</t>
@@ -894,6 +948,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>POp 2023
@@ -920,6 +975,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Pop 2023
@@ -958,6 +1014,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -973,6 +1030,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -987,6 +1045,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -1011,6 +1070,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Center-right or Right
@@ -1030,6 +1090,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Far-right
@@ -1047,6 +1108,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Abstention = 100 - Taux de participation</t>
@@ -1060,6 +1122,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -1084,6 +1147,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -1105,6 +1169,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2023)
@@ -1123,6 +1188,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -1140,6 +1206,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -1156,6 +1223,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -1172,6 +1240,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -1188,6 +1257,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -1204,6 +1274,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -1218,6 +1289,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en</t>
@@ -1231,6 +1303,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">East (pop 2023)
@@ -1256,6 +1329,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">West (pop 2023)
@@ -1280,6 +1354,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -1295,6 +1370,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">SOURCE : https://www.gov.pl/web/family/poland-ranks-second-in-the-eu-with-the-lowest-unemployment-rate-according-to-eurostat#:~:text=Poland%27s%20unemployment%20rate%20in%20December%202023%20was%202.7,only%20Malta%20with%20a%20rate%20of%202.4%20percent.
@@ -1313,6 +1389,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -1333,6 +1410,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Center-right or Right
@@ -1351,6 +1429,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Far-right
@@ -1368,6 +1447,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">miasta na prawach powiatu	</t>
@@ -1381,6 +1461,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Gminy bez miast na prawach powiatu</t>
@@ -1394,6 +1475,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -1409,6 +1491,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source - 2025
@@ -1423,6 +1506,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source - INE (2022)
@@ -1437,6 +1521,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2023</t>
@@ -1450,6 +1535,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en</t>
@@ -1463,6 +1549,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -1494,6 +1581,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -1518,6 +1606,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -1539,6 +1628,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -1562,6 +1652,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -1587,6 +1678,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -1602,6 +1694,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>avant(131)
@@ -1617,6 +1710,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -1640,6 +1734,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Center-right or Right
@@ -1658,6 +1753,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Far-right
@@ -1674,6 +1770,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -1689,6 +1786,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (Mid 2023) :
@@ -1703,6 +1801,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source(Mid 2023) :
@@ -1717,6 +1816,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (OCDE 2024) : 
@@ -1731,6 +1831,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">02/2025
@@ -1749,6 +1850,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>London
@@ -1764,6 +1866,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Southern England</t>
@@ -1777,6 +1880,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Central UK</t>
@@ -1790,6 +1894,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Northern England</t>
@@ -1803,6 +1908,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Northern UK</t>
@@ -1816,6 +1922,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -1831,6 +1938,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -1845,6 +1953,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">https://researchbriefings.files.parliament.uk/documents/CBP-10009/CBP-10009.pdf
@@ -1901,6 +2010,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Conservative
@@ -1955,6 +2065,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">UK Independence Party
@@ -1987,6 +2098,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>100 - Turnout</t>
@@ -2000,6 +2112,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">definition is in the code
@@ -2014,6 +2127,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -2029,6 +2143,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source : 2023 https://www.pxweb.bfs.admin.ch/pxweb/fr/px-x-0102010000_103/-/px-x-0102010000_103.px/table/tableViewLayout2/</t>
@@ -2042,6 +2157,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2023) :
@@ -2056,6 +2172,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -2070,6 +2187,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en
@@ -2084,6 +2202,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Suisse allemande (1)
@@ -2129,6 +2248,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Suisse Française (2)
@@ -2154,6 +2274,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Suisse Italienne (3)
@@ -2170,6 +2291,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -2185,6 +2307,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -2199,6 +2322,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">élections fédérales suisses de 2023
@@ -2221,6 +2345,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">PLR
@@ -2241,6 +2366,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">UDC
@@ -2256,6 +2382,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -2271,6 +2398,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://www.stat.go.jp/english/data/jinsui/2023np/index.html
@@ -2285,6 +2413,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Estimates as of October 1, 2023
@@ -2299,6 +2428,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (OCDE 2024): 
@@ -2313,6 +2443,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://gpseducation.oecd.org/IndicatorExplorer?plotter=h5&amp;query=37&amp;indicators=A003*A004*A005*A007*A008*A010*A011*A014*A594*A596*A595*A022*A023*A025*A026*A037*A113*A114*A115*A116*A117*A118*A119*A120*A121*A122*A123*A124*A125*A126*A127*A128*A129*A130*A131*A132*A187*A188*A189*A190*A191*A192*A193*A194*A195*A196*A197*A198*A199*A200*A288*A289*A290*A317*A318*A319*A320*A321*A322*A323*A324*A325*A326*A327*A328*A329*A351*A362*A375*A376*A377*A378*A379*A380*A381*A382*A383*A384*A385*A386*A028*A030*A031*A032*A033*A036*A064*A201*A202*A203*A210*A211*A212*A213*A214*A215*A216*A217*A218*A219*A220*A221*A222*A223*A224*A225*A226*A352*A353*A354*A357*A358*A359*A360*A361*C269*C270*C259*C260*C261*C262*C263*C264*C265*C266*C267*C268*C280*C281*C282*C283*C274*C275*C276*C277*C301*C279*C278*A012*A013*A021*A024*A330*A483*A484*A485*A486*A487*A488*A506*A507*A508*A509*A001*A019*A020*A642*A643*A731*A733*A737*A739*A742*A744*A746*A748*C351*C352*C353*C354*C355*C356*C357*C358*C198*C199*C200*C207*C359*C360*C361*C362*C482*C483*C484*C485*C486*C487*C488*C489*C490*C491*C492*C493*C494*C495*C496*A135*A136*A137*A138*A355*A356*C180*C181*C182*C183*C184*C185*C186*C187*C188*C211*C212*C213*C214*C223*C224*C225*C226*C245*C456*C457*C458*C459*C460*C463*C464*C465*C466*C467*C470*C471*C472*C473*C474*C014*C028*C057*C059*C062*C068*C137*C138*C166*C201*C202*C203*C204*C205*C206*C228*C251*C252*C253*C254*C384*C385*C386*C387*C388*C389*C390*C391*C392*C393*C394*C395*C396*C397*C398*C399</t>
@@ -2326,6 +2457,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>If the municipality type is a "shi" or a "ku".
@@ -2343,6 +2475,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>If the municipality type is a "cho", "machi", "mura" or "son"</t>
@@ -2356,6 +2489,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Chubu</t>
@@ -2369,6 +2503,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Kansai</t>
@@ -2382,6 +2517,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Kanto</t>
@@ -2395,6 +2531,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>North</t>
@@ -2408,6 +2545,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>South</t>
@@ -2421,6 +2559,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Educational attainment rate, completed upper secondary education or higher, population 25+ years, both sexes (%)
@@ -2439,6 +2578,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -2453,6 +2593,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Constituency : majoritarian system
@@ -2470,6 +2611,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">LDP
@@ -2487,6 +2629,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Sanseitō
@@ -2501,6 +2644,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -2516,6 +2660,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">https://rosstat.gov.ru/folder/12781
@@ -2531,6 +2676,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://rosstat.gov.ru/folder/12781 
@@ -2545,6 +2691,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>не имеющие
@@ -2559,6 +2706,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://rosstat.gov.ru/folder/12781
@@ -2574,6 +2722,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">https://городарф.рф/econ-areas.html  
@@ -2590,6 +2739,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Northwest</t>
@@ -2603,6 +2753,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Southwest</t>
@@ -2616,6 +2767,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>East</t>
@@ -2629,6 +2781,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://rosstat.gov.ru/vpn/2020/Tom3_Obrazovanie
@@ -2647,6 +2800,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2022) : 
@@ -2661,6 +2815,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2022
@@ -2675,6 +2830,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -2690,6 +2846,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
@@ -2712,6 +2869,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2022) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -2732,6 +2890,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -2750,6 +2909,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -2767,6 +2927,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -2784,6 +2945,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -2801,6 +2963,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -2818,6 +2981,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
@@ -2834,6 +2998,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">South (1)
@@ -2852,6 +3017,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>West (2):
@@ -2876,6 +3042,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Centre et  North (3)
@@ -2899,6 +3066,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Eastern Region (4)
@@ -2913,6 +3081,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Saudi Women
@@ -2933,6 +3102,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Non Saudi WOmen
@@ -2953,6 +3123,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Saudi Men
@@ -2972,6 +3143,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Non Saudi Men
@@ -2991,6 +3163,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2020
@@ -3005,6 +3178,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://www.stats.gov.sa/documents/20117/2435099/statistical_definitions_manual_english.pdf/9fd31cc6-c09b-a85a-abc8-6f3d1367105f?t=1733923142483
@@ -3027,6 +3201,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -3042,6 +3217,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) Census updated
@@ -3056,6 +3232,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2023) : 
@@ -3071,6 +3248,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2023</t>
@@ -3084,6 +3262,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">The most accurate data to deal with urbanity seems to be that from the census 2020
@@ -3101,6 +3280,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Northeast 
@@ -3115,6 +3295,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Midwest</t>
@@ -3128,6 +3309,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>South</t>
@@ -3141,6 +3323,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>West</t>
@@ -3154,6 +3337,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://www.census.gov/quickfacts/fact/table/US/RHI725223#RHI725223</t>
@@ -3167,6 +3351,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -3182,6 +3367,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source 2023 :
@@ -3196,6 +3382,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">https://www.reuters.com/graphics/USA-ELECTION/RESULTS/zjpqnemxwvx/
@@ -3214,6 +3401,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">% inscrits (par 1000)
@@ -3229,6 +3417,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>updated (year 2024)
@@ -4396,6 +4585,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Percentage of population in the same subgroup</t>
@@ -4409,6 +4599,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Unit of measure: 
@@ -4423,6 +4614,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Unit of measure: 
@@ -4437,6 +4629,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Base : Votants </t>
@@ -4450,6 +4643,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Corrigé par le taux de participation</t>
@@ -4463,6 +4657,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source : https://www.eea.europa.eu/data-and-maps/data/external/degree-of-urbanisation-degurba</t>
@@ -4476,6 +4671,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source(year 2025) : INSEE
@@ -4490,6 +4686,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source(year 2025) : INSEE
@@ -4506,6 +4703,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source(year 2025) : INSEE
@@ -4522,6 +4720,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Year 2025
@@ -4536,6 +4735,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -4550,6 +4750,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">2015 data - best available
@@ -4565,6 +4766,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Ile de France
@@ -4581,6 +4783,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">North and East
@@ -4596,6 +4799,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>South West
@@ -4610,6 +4814,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>South-East
@@ -4624,6 +4829,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Other regions
@@ -4638,6 +4844,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -4653,6 +4860,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -4668,6 +4876,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">2023
@@ -4683,6 +4892,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -4708,6 +4918,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -4722,6 +4933,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
@@ -4736,6 +4948,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -4750,6 +4963,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -4764,6 +4978,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -4778,6 +4993,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">% Inscrits
@@ -4792,6 +5008,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">same definition as 2020
@@ -4806,6 +5023,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2023) : Destatis Statistisches Bundesamt
@@ -4820,6 +5038,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source : (Year 2023)
@@ -4834,6 +5053,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -4848,6 +5068,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -4862,6 +5083,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -4876,6 +5098,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -4890,6 +5113,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source ( year 2023) :  Destatis Statistisches Bundesamt
@@ -4904,6 +5128,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -4918,6 +5143,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en</t>
@@ -4931,6 +5157,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
@@ -4948,6 +5175,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Southern
@@ -4963,6 +5191,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">3 -Others [Northern, Western, Central]
@@ -4978,6 +5207,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://data-explorer.oecd.org/vis?tm=inactivity&amp;pg=0&amp;snb=17&amp;vw=tb&amp;df[ds]=dsDisseminateFinalDMZ&amp;df[id]=DSD_EAG_LSO_EA%40DF_LSO_NEAC_INAC&amp;df[ag]=OECD.EDU.IMEP&amp;df[vs]=1.0&amp;dq=FRA%2BDEU%2BITA%2BJPN%2BLVA%2BMEX%2BPOL%2BESP%2BCHE%2BGBR%2BUSA%2BOECD%2BIND%2BROU%2BZAF._T.Y25T64._T..........OBS...A&amp;lom=LASTNOBSERVATIONS&amp;lo=1&amp;pd=2020%2C2023&amp;to[TIME_PERIOD]=true</t>
@@ -4991,6 +5221,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -5005,6 +5236,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Bundestagswahl 2025 : 
@@ -5036,6 +5268,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Bundestagswahl 2025 : </t>
@@ -5049,6 +5282,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Bundestagswahl 2025 : </t>
@@ -5062,6 +5296,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Bundestagswahl 2025 : 
@@ -5093,6 +5328,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Center-right or right
@@ -5121,6 +5357,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Far right
@@ -5137,6 +5374,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Abstention = Persons entitled to vote
@@ -5153,6 +5391,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -5167,6 +5406,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  Istituto Nazionale di Statistica
@@ -5187,6 +5427,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -5206,6 +5447,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -5220,6 +5462,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -5234,6 +5477,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -5248,6 +5492,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -5262,6 +5507,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  Istituto Nazionale di Statistica
@@ -5276,6 +5522,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -5290,6 +5537,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en</t>
@@ -5303,6 +5551,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>POp 2023
@@ -5329,6 +5578,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Pop 2023
@@ -5367,6 +5617,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -5382,6 +5633,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -5396,6 +5648,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -5420,6 +5673,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Center-right or Right
@@ -5439,6 +5693,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Far-right
@@ -5456,6 +5711,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Abstention = 100 - Taux de participation</t>
@@ -5469,6 +5725,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -5493,6 +5750,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -5514,6 +5772,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2023)
@@ -5532,6 +5791,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -5549,6 +5809,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -5565,6 +5826,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -5581,6 +5843,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -5597,6 +5860,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (2023) : Statistics Poland - Główny Urząd Statystyczny
@@ -5613,6 +5877,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -5627,6 +5892,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en</t>
@@ -5640,6 +5906,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">East (pop 2023)
@@ -5665,6 +5932,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">West (pop 2023)
@@ -5689,6 +5957,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -5704,6 +5973,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">SOURCE : https://www.gov.pl/web/family/poland-ranks-second-in-the-eu-with-the-lowest-unemployment-rate-according-to-eurostat#:~:text=Poland%27s%20unemployment%20rate%20in%20December%202023%20was%202.7,only%20Malta%20with%20a%20rate%20of%202.4%20percent.
@@ -5722,6 +5992,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -5742,6 +6013,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Center-right or Right
@@ -5760,6 +6032,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Far-right
@@ -5777,6 +6050,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">miasta na prawach powiatu	</t>
@@ -5790,6 +6064,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Gminy bez miast na prawach powiatu</t>
@@ -5803,6 +6078,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -5818,6 +6094,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source - 2025
@@ -5832,6 +6109,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source - INE (2022)
@@ -5846,6 +6124,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2023</t>
@@ -5859,6 +6138,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en</t>
@@ -5872,6 +6152,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -5903,6 +6184,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -5927,6 +6209,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -5948,6 +6231,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -5971,6 +6255,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source  :
@@ -5996,6 +6281,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -6011,6 +6297,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>avant(131)
@@ -6026,6 +6313,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Élections européennes 2024 :
@@ -6049,6 +6337,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Center-right or Right
@@ -6067,6 +6356,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Far-right
@@ -6083,6 +6373,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -6098,6 +6389,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (Mid 2023) :
@@ -6112,6 +6404,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source(Mid 2023) :
@@ -6126,6 +6419,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (OCDE 2024) : 
@@ -6140,6 +6434,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">02/2025
@@ -6158,6 +6453,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>London
@@ -6173,6 +6469,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Southern England</t>
@@ -6186,6 +6483,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Central UK</t>
@@ -6199,6 +6497,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Northern England</t>
@@ -6212,6 +6511,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Northern UK</t>
@@ -6225,6 +6525,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -6240,6 +6541,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -6254,6 +6556,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">https://researchbriefings.files.parliament.uk/documents/CBP-10009/CBP-10009.pdf
@@ -6310,6 +6613,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Conservative
@@ -6364,6 +6668,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">UK Independence Party
@@ -6396,6 +6701,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>100 - Turnout</t>
@@ -6409,6 +6715,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">definition is in the code
@@ -6423,6 +6730,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -6438,6 +6746,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source : 2023 https://www.pxweb.bfs.admin.ch/pxweb/fr/px-x-0102010000_103/-/px-x-0102010000_103.px/table/tableViewLayout2/</t>
@@ -6451,6 +6760,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2023) :
@@ -6465,6 +6775,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2024
@@ -6479,6 +6790,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2024 : https://ec.europa.eu/eurostat/databrowser/view/ilc_lvho01__custom_16633018/default/table?lang=en
@@ -6493,6 +6805,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Suisse allemande (1)
@@ -6538,6 +6851,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Suisse Française (2)
@@ -6563,6 +6877,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Suisse Italienne (3)
@@ -6579,6 +6894,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -6594,6 +6910,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -6608,6 +6925,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">élections fédérales suisses de 2023
@@ -6630,6 +6948,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">PLR
@@ -6650,6 +6969,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">UDC
@@ -6665,6 +6985,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -6680,6 +7001,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://www.stat.go.jp/english/data/jinsui/2023np/index.html
@@ -6694,6 +7016,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Estimates as of October 1, 2023
@@ -6708,6 +7031,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (OCDE 2024): 
@@ -6722,6 +7046,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://gpseducation.oecd.org/IndicatorExplorer?plotter=h5&amp;query=37&amp;indicators=A003*A004*A005*A007*A008*A010*A011*A014*A594*A596*A595*A022*A023*A025*A026*A037*A113*A114*A115*A116*A117*A118*A119*A120*A121*A122*A123*A124*A125*A126*A127*A128*A129*A130*A131*A132*A187*A188*A189*A190*A191*A192*A193*A194*A195*A196*A197*A198*A199*A200*A288*A289*A290*A317*A318*A319*A320*A321*A322*A323*A324*A325*A326*A327*A328*A329*A351*A362*A375*A376*A377*A378*A379*A380*A381*A382*A383*A384*A385*A386*A028*A030*A031*A032*A033*A036*A064*A201*A202*A203*A210*A211*A212*A213*A214*A215*A216*A217*A218*A219*A220*A221*A222*A223*A224*A225*A226*A352*A353*A354*A357*A358*A359*A360*A361*C269*C270*C259*C260*C261*C262*C263*C264*C265*C266*C267*C268*C280*C281*C282*C283*C274*C275*C276*C277*C301*C279*C278*A012*A013*A021*A024*A330*A483*A484*A485*A486*A487*A488*A506*A507*A508*A509*A001*A019*A020*A642*A643*A731*A733*A737*A739*A742*A744*A746*A748*C351*C352*C353*C354*C355*C356*C357*C358*C198*C199*C200*C207*C359*C360*C361*C362*C482*C483*C484*C485*C486*C487*C488*C489*C490*C491*C492*C493*C494*C495*C496*A135*A136*A137*A138*A355*A356*C180*C181*C182*C183*C184*C185*C186*C187*C188*C211*C212*C213*C214*C223*C224*C225*C226*C245*C456*C457*C458*C459*C460*C463*C464*C465*C466*C467*C470*C471*C472*C473*C474*C014*C028*C057*C059*C062*C068*C137*C138*C166*C201*C202*C203*C204*C205*C206*C228*C251*C252*C253*C254*C384*C385*C386*C387*C388*C389*C390*C391*C392*C393*C394*C395*C396*C397*C398*C399</t>
@@ -6735,6 +7060,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>If the municipality type is a "shi" or a "ku".
@@ -6752,6 +7078,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>If the municipality type is a "cho", "machi", "mura" or "son"</t>
@@ -6765,6 +7092,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Chubu</t>
@@ -6778,6 +7106,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Kansai</t>
@@ -6791,6 +7120,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Kanto</t>
@@ -6804,6 +7134,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>North</t>
@@ -6817,6 +7148,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>South</t>
@@ -6830,6 +7162,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Educational attainment rate, completed upper secondary education or higher, population 25+ years, both sexes (%)
@@ -6848,6 +7181,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2023) : 
@@ -6862,6 +7196,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Constituency : majoritarian system
@@ -6879,6 +7214,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">LDP
@@ -6896,6 +7232,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Sanseitō
@@ -6910,6 +7247,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -6925,6 +7263,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">https://rosstat.gov.ru/folder/12781
@@ -6940,6 +7279,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://rosstat.gov.ru/folder/12781 
@@ -6954,6 +7294,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>не имеющие
@@ -6968,6 +7309,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://rosstat.gov.ru/folder/12781
@@ -6983,6 +7325,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">https://городарф.рф/econ-areas.html  
@@ -6999,6 +7342,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Northwest</t>
@@ -7012,6 +7356,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Southwest</t>
@@ -7025,6 +7370,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>East</t>
@@ -7038,6 +7384,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://rosstat.gov.ru/vpn/2020/Tom3_Obrazovanie
@@ -7056,6 +7403,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (2022) : 
@@ -7070,6 +7418,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2022
@@ -7084,6 +7433,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -7099,6 +7449,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
@@ -7121,6 +7472,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2022) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -7141,6 +7493,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -7159,6 +7512,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -7176,6 +7530,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -7193,6 +7548,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -7210,6 +7566,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2024) :  General Authority for Statistics (GASTAT)  / Ministry of Economy and Planning
@@ -7227,6 +7584,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
@@ -7243,6 +7601,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">South (1)
@@ -7261,6 +7620,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>West (2):
@@ -7285,6 +7645,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Centre et  North (3)
@@ -7308,6 +7669,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Eastern Region (4)
@@ -7322,6 +7684,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Saudi Women
@@ -7342,6 +7705,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Non Saudi WOmen
@@ -7362,6 +7726,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Saudi Men
@@ -7381,6 +7746,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Non Saudi Men
@@ -7400,6 +7766,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>2020
@@ -7414,6 +7781,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://www.stats.gov.sa/documents/20117/2435099/statistical_definitions_manual_english.pdf/9fd31cc6-c09b-a85a-abc8-6f3d1367105f?t=1733923142483
@@ -7436,6 +7804,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>source(2023 ): World Population Prospects 2024 File POP/03-1: Total population (both sexes combined) by select age group, region, subregion and country, annually for 1950-2100 (thousands)
@@ -7451,6 +7820,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source (year 2024) Census updated
@@ -7465,6 +7835,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Source (year 2023) : 
@@ -7480,6 +7851,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>OECD 2023</t>
@@ -7493,6 +7865,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">The most accurate data to deal with urbanity seems to be that from the census 2020
@@ -7510,6 +7883,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Northeast 
@@ -7524,6 +7898,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Midwest</t>
@@ -7537,6 +7912,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>South</t>
@@ -7550,6 +7926,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>West</t>
@@ -7563,6 +7940,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://www.census.gov/quickfacts/fact/table/US/RHI725223#RHI725223</t>
@@ -7576,6 +7954,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Age: From 25 to 64 years
@@ -7591,6 +7970,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Source 2023 :
@@ -7605,6 +7985,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">https://www.reuters.com/graphics/USA-ELECTION/RESULTS/zjpqnemxwvx/
@@ -7623,6 +8004,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">% inscrits (par 1000)
@@ -7638,6 +8020,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>updated (year 2024)
@@ -7652,6 +8035,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Regions (east)
@@ -7676,6 +8060,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">SOurce (pop 2023) 
@@ -7697,6 +8082,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
@@ -7717,6 +8103,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Regions (west-south)
@@ -7735,6 +8122,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">North-West
@@ -7753,6 +8141,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>North-East
@@ -7774,6 +8163,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Center
@@ -7790,6 +8180,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">South
@@ -7809,6 +8200,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://datasaudi.sa/en/data-explorer?cube=non_saudi_population&amp;locale=en&amp;drilldowns=Year%2CSex%2CCountry&amp;measures=Population&amp;include=Year%3A2022%3BSex%3A&amp;limit=100%2C0&amp;panel=table</t>
@@ -7822,6 +8214,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>cities</t>
@@ -7835,6 +8228,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Saudi Women</t>
@@ -7848,6 +8242,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Non saudi women</t>
@@ -7861,6 +8256,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Saudi Man
@@ -7875,6 +8271,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>22/04/2025 : +10% Man and Woman Saudi; just Q4</t>
@@ -7888,6 +8285,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve"> +10% Man  Saudi
@@ -7904,6 +8302,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>https://datasaudi.sa/en/data-explorer?cube=non_saudi_population&amp;locale=en&amp;drilldowns=Year%2CSex%2CCountry&amp;measures=Population&amp;include=Year%3A2022%3BSex%3A&amp;limit=100%2C0&amp;panel=table</t>
@@ -14792,6 +15191,7 @@
         <sz val="10"/>
         <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>Statistics Poland - Local Data Bank</t>
     </r>
@@ -14830,6 +15230,7 @@
         <sz val="10"/>
         <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>Glossary of Statistical Terms Details</t>
     </r>
@@ -14922,7 +15323,7 @@
     <numFmt numFmtId="167" formatCode="#\ ###\ ###\ ##0;\-#\ ###\ ###\ ##0;0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="60">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15215,89 +15616,98 @@
       <sz val="11"/>
       <color rgb="FF181A1B"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF181A1B"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF181A1B"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF181A1B"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -15305,18 +15715,21 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -15663,14 +16076,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="168" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="168" fontId="47" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>

--- a/questionnaire/sources.xlsx
+++ b/questionnaire/sources.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="735" windowWidth="12960" windowHeight="5865" tabRatio="831" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="735" windowWidth="12960" windowHeight="5865" tabRatio="831"/>
   </bookViews>
   <sheets>
     <sheet name="Figures" sheetId="1" r:id="rId1"/>
@@ -8314,7 +8314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6857" uniqueCount="2325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6862" uniqueCount="2328">
   <si>
     <t>Country</t>
   </si>
@@ -15310,6 +15310,15 @@
   </si>
   <si>
     <t>(quotas_count!B2+quotas_count!E2)/D16</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>RMB 180</t>
+  </si>
+  <si>
+    <t>RMB 250</t>
   </si>
 </sst>
 </file>
@@ -17791,6 +17800,9 @@
       <c r="O1" s="1" t="s">
         <v>910</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>2325</v>
+      </c>
     </row>
     <row r="2" spans="1:24" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
@@ -19004,7 +19016,9 @@
         <v>1668</v>
       </c>
       <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
+      <c r="P31" s="55">
+        <v>6.71</v>
+      </c>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
@@ -19254,6 +19268,12 @@
         <v>293</v>
       </c>
       <c r="L36" t="s">
+        <v>293</v>
+      </c>
+      <c r="M36" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="P36" s="55" t="s">
         <v>293</v>
       </c>
       <c r="R36" s="7"/>
@@ -19402,7 +19422,9 @@
       </c>
       <c r="N40" s="39"/>
       <c r="O40" s="39"/>
-      <c r="P40" s="39"/>
+      <c r="P40" s="39" t="s">
+        <v>2326</v>
+      </c>
       <c r="Q40" s="39"/>
       <c r="R40" s="7"/>
     </row>
@@ -19460,7 +19482,10 @@
       </c>
       <c r="N41" s="39"/>
       <c r="O41" s="39"/>
-      <c r="P41" s="39"/>
+      <c r="P41" s="4">
+        <f>P31*P43</f>
+        <v>181.17</v>
+      </c>
       <c r="Q41" s="39"/>
       <c r="R41" s="7"/>
     </row>
@@ -19531,6 +19556,9 @@
       <c r="M43" s="2">
         <v>88</v>
       </c>
+      <c r="P43">
+        <v>27</v>
+      </c>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="1" t="s">
@@ -19572,6 +19600,9 @@
       <c r="M44" s="1">
         <v>88</v>
       </c>
+      <c r="P44" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="1" t="s">
@@ -19604,6 +19635,9 @@
       <c r="J45" s="1">
         <v>48</v>
       </c>
+      <c r="P45" s="1">
+        <v>27</v>
+      </c>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="1" t="s">
@@ -19645,6 +19679,9 @@
       <c r="M46" s="4">
         <v>35.74</v>
       </c>
+      <c r="P46" s="4">
+        <v>46</v>
+      </c>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="1" t="s">
@@ -19686,6 +19723,9 @@
       <c r="M47" s="4">
         <v>22.308</v>
       </c>
+      <c r="P47" s="7">
+        <v>37</v>
+      </c>
     </row>
     <row r="48" spans="1:18">
       <c r="A48" s="1" t="s">
@@ -19739,6 +19779,10 @@
         <f t="shared" si="4"/>
         <v>35.74</v>
       </c>
+      <c r="P48" s="4">
+        <f>P46*P31</f>
+        <v>308.66000000000003</v>
+      </c>
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="1" t="s">
@@ -19792,6 +19836,10 @@
         <f t="shared" si="5"/>
         <v>22.308</v>
       </c>
+      <c r="P49" s="7">
+        <f>P47*P31</f>
+        <v>248.27</v>
+      </c>
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="1" t="s">
@@ -19831,6 +19879,9 @@
       <c r="M50" t="s">
         <v>932</v>
       </c>
+      <c r="P50" t="s">
+        <v>2327</v>
+      </c>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="1" t="s">
@@ -19869,6 +19920,9 @@
       </c>
       <c r="M51" s="39" t="s">
         <v>903</v>
+      </c>
+      <c r="P51">
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:18">
